--- a/Design modeling (Recovered).xlsx
+++ b/Design modeling (Recovered).xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Project\Github\DataOps_pipeline_HomeCredit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0691C4F-3A0A-4FA7-A3EF-A1B8F878F2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083231A1-B84E-4203-B898-E2FEF4D3AC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE4BAE36-A8E2-455E-949A-C8F143B5D163}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{EE4BAE36-A8E2-455E-949A-C8F143B5D163}"/>
   </bookViews>
   <sheets>
     <sheet name="danh sách bảng draft" sheetId="1" r:id="rId1"/>
-    <sheet name="Define Table Type" sheetId="2" r:id="rId2"/>
+    <sheet name="Define Table Context" sheetId="2" r:id="rId2"/>
     <sheet name="Define Grain" sheetId="4" r:id="rId3"/>
-    <sheet name="Build Table" sheetId="6" r:id="rId4"/>
+    <sheet name="Define Modeling &amp; STTMapping" sheetId="6" r:id="rId4"/>
     <sheet name="draft" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Define Table Type'!$A$1:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Define Table Context'!$A$1:$E$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="408">
   <si>
     <t>SK_ID_CURR: ID duy nhất của khách hàng / khoản vay trong sample.</t>
   </si>
@@ -613,9 +613,6 @@
     <t>Type 1</t>
   </si>
   <si>
-    <t>Giới tính (M, F, XNA)</t>
-  </si>
-  <si>
     <t>Type 2</t>
   </si>
   <si>
@@ -853,9 +850,6 @@
     <t>Tháng tương đối (-1, -2...)</t>
   </si>
   <si>
-    <t>Dim_Application_Stattus</t>
-  </si>
-  <si>
     <t>Status_SK</t>
   </si>
   <si>
@@ -863,6 +857,405 @@
   </si>
   <si>
     <t>Hạn mức thẻ.</t>
+  </si>
+  <si>
+    <t>Column_Type</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>SCD_type</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Mỗi dòng đại diện cho theo dõi trạng thái khoản vay ngoài tổ chức do CIC cung cấp</t>
+  </si>
+  <si>
+    <t>Giới tính (M, F)</t>
+  </si>
+  <si>
+    <t>Data_Type</t>
+  </si>
+  <si>
+    <t>Behavior_SCD</t>
+  </si>
+  <si>
+    <t>Source_Table.Column</t>
+  </si>
+  <si>
+    <t>Transformation_Logic</t>
+  </si>
+  <si>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>Tự tăng (Identity/Sequence) hoặc monotonically_increasing_id()</t>
+  </si>
+  <si>
+    <t>application.SK_ID_CURR</t>
+  </si>
+  <si>
+    <t>CAST(SK_ID_CURR AS STRING)</t>
+  </si>
+  <si>
+    <t>application.DAYS_BIRTH</t>
+  </si>
+  <si>
+    <t>CAST(DAYS_BIRTH AS INT)</t>
+  </si>
+  <si>
+    <t>application.CODE_GENDER</t>
+  </si>
+  <si>
+    <t>COALESCE(UPPER(TRIM(CODE_GENDER)), 'XNA')</t>
+  </si>
+  <si>
+    <t>application.NAME_FAMILY_STATUS</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(NAME_FAMILY_STATUS), 'Unknown')</t>
+  </si>
+  <si>
+    <t>application.NAME_EDUCATION_TYPE</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(NAME_EDUCATION_TYPE), 'Unknown')</t>
+  </si>
+  <si>
+    <t>application.REGION_RATING_CLIENT</t>
+  </si>
+  <si>
+    <t>CAST(REGION_RATING_CLIENT AS SMALLINT)</t>
+  </si>
+  <si>
+    <t>application.AMT_INCOME_TOTAL</t>
+  </si>
+  <si>
+    <t>ROUND(CAST(AMT_INCOME_TOTAL AS DECIMAL(18,2)), 2)</t>
+  </si>
+  <si>
+    <t>application.DAYS_EMPLOYED</t>
+  </si>
+  <si>
+    <t>CAST(DAYS_EMPLOYED AS INT)</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>System Timestamp</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP() khi insert dòng mới</t>
+  </si>
+  <si>
+    <t>TIMESTAMP('9999-12-31 23:59:59') khi tạo mới; cập nhật thành CURRENT_TIMESTAMP() khi dòng bị expire</t>
+  </si>
+  <si>
+    <t>System Flag</t>
+  </si>
+  <si>
+    <t>'Y' cho bản ghi mới; đổi thành 'N' khi có thay đổi thuộc tính SCD2</t>
+  </si>
+  <si>
+    <t>DENSE_RANK() hoặc Sequence</t>
+  </si>
+  <si>
+    <t>application.NAME_CONTRACT_TYPE</t>
+  </si>
+  <si>
+    <t>DISTINCT TRIM(NAME_CONTRACT_TYPE)</t>
+  </si>
+  <si>
+    <t>Tên chuẩn hóa hiển thị cho báo cáo</t>
+  </si>
+  <si>
+    <t>Dim_Application_Status</t>
+  </si>
+  <si>
+    <t>Tự sinh khóa nguyên (1, 2, 3...)</t>
+  </si>
+  <si>
+    <t>previous_application.NAME_CONTRACT_STATUS</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(NAME_CONTRACT_STATUS), 'Unknown')</t>
+  </si>
+  <si>
+    <t>previous_application.CODE_REJECT_REASON</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(CODE_REJECT_REASON), 'XAP')</t>
+  </si>
+  <si>
+    <t>DEFINE ALL TABLE TARGET</t>
+  </si>
+  <si>
+    <t>Append-only</t>
+  </si>
+  <si>
+    <t>F.abs(F.hash(F.col("Loan_ID")))</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Customer WHERE Customer_BK = SK_ID_CURR AND Is_Current_Flag = 'Y'. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>previous_application.DAYS_DECISION</t>
+  </si>
+  <si>
+    <t>date_format(date_add('2020-01-01', DAYS_DECISION), 'yyyyMMdd') CAST AS INT. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Contract_Type qua Contract_Type_Code. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>previous_application.NAME_CONTRACT_STATUS, CODE_REJECT_REASON</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Application_Status qua cặp trạng thái + lý do. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>application.SK_ID_CURR / previous_application.SK_ID_PREV</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(SK_ID_PREV AS STRING), CAST(SK_ID_CURR AS STRING))</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>previous_application.AMT_APPLICATION</t>
+  </si>
+  <si>
+    <t>CAST(AMT_APPLICATION AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>application.AMT_CREDIT</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(AMT_CREDIT AS DECIMAL(18,2)), 0.00)</t>
+  </si>
+  <si>
+    <t>application.AMT_ANNUITY</t>
+  </si>
+  <si>
+    <t>CAST(AMT_ANNUITY AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>application.AMT_GOODS_PRICE</t>
+  </si>
+  <si>
+    <t>CAST(AMT_GOODS_PRICE AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>application.TARGET</t>
+  </si>
+  <si>
+    <t>CAST(TARGET AS SMALLINT)</t>
+  </si>
+  <si>
+    <t>F.abs(F.hash(F.concat_ws('_', F.col('SK_ID_PREV'), F.col('NUM_INSTALMENT_NUMBER'))))</t>
+  </si>
+  <si>
+    <t>installments_payments.SK_ID_PREV</t>
+  </si>
+  <si>
+    <t>Join qua previous_application lấy SK_ID_CURR -&gt; Lookup Dim_Customer. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>installments_payments.DAYS_INSTALMENT</t>
+  </si>
+  <si>
+    <t>date_format(date_add('2020-01-01', DAYS_INSTALMENT), 'yyyyMMdd') CAST AS INT. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>installments_payments.DAYS_ENTRY_PAYMENT</t>
+  </si>
+  <si>
+    <t>date_format(date_add('2020-01-01', DAYS_ENTRY_PAYMENT), 'yyyyMMdd') CAST AS INT. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>CAST(SK_ID_PREV AS STRING)</t>
+  </si>
+  <si>
+    <t>installments_payments.NUM_INSTALMENT_NUMBER</t>
+  </si>
+  <si>
+    <t>CAST(NUM_INSTALMENT_NUMBER AS INT)</t>
+  </si>
+  <si>
+    <t>installments_payments.AMT_INSTALMENT</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(AMT_INSTALMENT AS DECIMAL(18,2)), 0.00)</t>
+  </si>
+  <si>
+    <t>installments_payments.AMT_PAYMENT</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(AMT_PAYMENT AS DECIMAL(18,2)), 0.00)</t>
+  </si>
+  <si>
+    <t>COALESCE(AMT_INSTALMENT, 0) - COALESCE(AMT_PAYMENT, 0)</t>
+  </si>
+  <si>
+    <t>CASE WHEN DAYS_ENTRY_PAYMENT &gt; DAYS_INSTALMENT THEN CAST(DAYS_ENTRY_PAYMENT - DAYS_INSTALMENT AS INT) ELSE 0 END</t>
+  </si>
+  <si>
+    <t>DEFINE ALL TABLE SOURCE - LOGIC TRANSFORMATION</t>
+  </si>
+  <si>
+    <t>Credit_Balance_SK</t>
+  </si>
+  <si>
+    <t>Upsert / Snapshot</t>
+  </si>
+  <si>
+    <t>F.abs(F.hash(F.concat_ws('_', F.col('SK_ID_PREV'), F.col('MONTHS_BALANCE'))))</t>
+  </si>
+  <si>
+    <t>credit_card_balance.SK_ID_CURR</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Customer qua SK_ID_CURR. Nếu NULL gán -1</t>
+  </si>
+  <si>
+    <t>credit_card_balance.MONTHS_BALANCE</t>
+  </si>
+  <si>
+    <t>Quy đổi MONTHS_BALANCE (-1, -2) thành ngày cuối tháng tương ứng định dạng YYYYMMDD</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Contract_Type với mã 'Revolving loans'</t>
+  </si>
+  <si>
+    <t>Card_Account_ID</t>
+  </si>
+  <si>
+    <t>credit_card_balance.SK_ID_PREV</t>
+  </si>
+  <si>
+    <t>credit_card_balance.AMT_BALANCE</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(AMT_BALANCE AS DECIMAL(18,2)), 0.00)</t>
+  </si>
+  <si>
+    <t>credit_card_balance.AMT_CREDIT_LIMIT_ACTUAL</t>
+  </si>
+  <si>
+    <t>CAST(AMT_CREDIT_LIMIT_ACTUAL AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>credit_card_balance.AMT_PAYMENT_TOTAL_CURRENT</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(AMT_PAYMENT_TOTAL_CURRENT AS DECIMAL(18,2)), 0.00)</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.SK_ID_CURR</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.MONTHS_BALANCE</t>
+  </si>
+  <si>
+    <t>Quy đổi MONTHS_BALANCE thành YYYYMMDD cuối tháng</t>
+  </si>
+  <si>
+    <t>Lookup Dim_Contract_Type với mã 'Cash loans'</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.SK_ID_PREV</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.CNT_INSTALMENT</t>
+  </si>
+  <si>
+    <t>CAST(CNT_INSTALMENT AS SMALLINT)</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.CNT_INSTALMENT_FUTURE</t>
+  </si>
+  <si>
+    <t>CAST(CNT_INSTALMENT_FUTURE AS SMALLINT)</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.SK_DPD</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(SK_DPD AS INT), 0)</t>
+  </si>
+  <si>
+    <t>POS_CASH_balance.SK_DPD_DEF</t>
+  </si>
+  <si>
+    <t>COALESCE(CAST(SK_DPD_DEF AS INT), 0)</t>
+  </si>
+  <si>
+    <t>F.abs(F.hash(F.col('SK_ID_BUREAU')))</t>
+  </si>
+  <si>
+    <t>bureau.SK_ID_CURR</t>
+  </si>
+  <si>
+    <t>bureau.DAYS_CREDIT</t>
+  </si>
+  <si>
+    <t>date_format(date_add('2020-01-01', DAYS_CREDIT), 'yyyyMMdd') CAST AS INT</t>
+  </si>
+  <si>
+    <t>bureau.SK_ID_BUREAU</t>
+  </si>
+  <si>
+    <t>CAST(SK_ID_BUREAU AS STRING)</t>
+  </si>
+  <si>
+    <t>bureau.CREDIT_ACTIVE</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(CREDIT_ACTIVE), 'Unknown')</t>
+  </si>
+  <si>
+    <t>bureau.CREDIT_TYPE</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(CREDIT_TYPE), 'Unknown')</t>
+  </si>
+  <si>
+    <t>bureau.AMT_CREDIT_SUM</t>
+  </si>
+  <si>
+    <t>CAST(AMT_CREDIT_SUM AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>bureau.AMT_CREDIT_MAX_OVERDUE</t>
+  </si>
+  <si>
+    <t>CAST(AMT_CREDIT_MAX_OVERDUE AS DECIMAL(18,2))</t>
+  </si>
+  <si>
+    <t>F.abs(F.hash(F.concat_ws('_', F.col('SK_BUREAU_ID'), F.col('MONTHS_BALANCE'))))</t>
+  </si>
+  <si>
+    <t>bureau_balance.MONTHS_BALANCE</t>
+  </si>
+  <si>
+    <t>bureau_balance.SK_BUREAU_ID</t>
+  </si>
+  <si>
+    <t>CAST(SK_BUREAU_ID AS STRING)</t>
+  </si>
+  <si>
+    <t>bureau_balance.STATUS</t>
+  </si>
+  <si>
+    <t>COALESCE(TRIM(STATUS), 'X')</t>
+  </si>
+  <si>
+    <t>CAST(MONTHS_BALANCE AS SMALLINT)</t>
   </si>
 </sst>
 </file>
@@ -898,7 +1291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -917,6 +1310,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -930,7 +1341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -939,16 +1350,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -969,12 +1396,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6BFDFBD1-3A77-4A4D-BBD2-5A949B6FEC85}" name="Table1" displayName="Table1" ref="A1:K1048572" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89A5201B-8218-4C76-99DE-01E98D9CD842}" name="Table2" displayName="Table2" ref="A1:E48" totalsRowShown="0">
+  <autoFilter ref="A1:E48" xr:uid="{DB9FF7A4-C762-4C9E-945E-EB2964C2D30A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{404620C8-3FD1-428D-B8D5-0E4CA9D1FB7A}" name="Table_Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{DC0778DD-A548-4FE5-BAB1-66EE0A9A0DE2}" name="Business Context" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{34606EE9-E554-4851-8485-66B661889216}" name="Column_name"/>
+    <tableColumn id="4" xr3:uid="{F0606F0D-72D6-432B-B258-6DEF15293A4C}" name="Category"/>
+    <tableColumn id="5" xr3:uid="{551D29BC-114C-477B-9EEE-1942DC07DFA1}" name="Thông tin thêm"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{310A1FC2-594B-46D9-ADFA-D4F80CB991D2}" name="Table3" displayName="Table3" ref="A1:G6" totalsRowShown="0">
+  <autoFilter ref="A1:G6" xr:uid="{310A1FC2-594B-46D9-ADFA-D4F80CB991D2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{10EB8A1C-A795-48F8-8160-FFA4A36BCAB3}" name="Process_ID"/>
+    <tableColumn id="2" xr3:uid="{1DBE4624-FB5B-4737-A1E9-EE1F93AC52C9}" name="Business_Process_Name"/>
+    <tableColumn id="3" xr3:uid="{46C88194-0854-416F-B4EC-576DE70C1C9D}" name="Business_Description"/>
+    <tableColumn id="4" xr3:uid="{F4EDD5C9-BFF7-4AF3-A730-C4544149DDD5}" name="Source_Systems_Tables"/>
+    <tableColumn id="5" xr3:uid="{8D487873-A7A3-49CC-B5EF-D44DA3419B3A}" name="Fact_Table_Intended"/>
+    <tableColumn id="6" xr3:uid="{4C82BC37-342B-4F1A-B7E0-3901212AC874}" name="Fact_Type"/>
+    <tableColumn id="7" xr3:uid="{E2D23D7F-DE33-4C41-9C68-1689CE05F61E}" name="Primary_Business_KPI"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6BFDFBD1-3A77-4A4D-BBD2-5A949B6FEC85}" name="Table1" displayName="Table1" ref="A2:K1048570" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{61B3204D-0EB0-4FE4-8FA4-1E48EBCABA9C}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{75FE2883-7BBD-4CD3-BDE6-DDF739C868B6}" name="Column2"/>
     <tableColumn id="3" xr3:uid="{63500B9B-EF9E-4444-ABAB-4E68E8152CCE}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{A8F02D5B-BFB3-4819-9229-7A0B2DBE2529}" name="Column4" headerRowDxfId="1" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{A8F02D5B-BFB3-4819-9229-7A0B2DBE2529}" name="Column4" headerRowDxfId="3" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{62253313-2691-4D8C-94AE-8797984A96F2}" name="Column5"/>
     <tableColumn id="6" xr3:uid="{8DF0BEF0-8BB5-4624-AAB0-2D56C6EC4505}" name="Column6"/>
     <tableColumn id="7" xr3:uid="{4C817600-19A3-48DE-9879-954DE407762C}" name="Column7"/>
@@ -1285,13 +1742,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EFD2E2-DB50-4EFD-B0E6-20C6A1143407}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="98.85546875" customWidth="1"/>
-    <col min="3" max="3" width="84.140625" customWidth="1"/>
+    <col min="1" max="1" width="98.81640625" customWidth="1"/>
+    <col min="3" max="3" width="84.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1307,7 +1764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1315,32 +1772,32 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1356,7 +1813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1364,7 +1821,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1372,92 +1829,92 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -1465,7 +1922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -1473,22 +1930,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
         <v>40</v>
       </c>
@@ -1502,16 +1959,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9FF7A4-C762-4C9E-945E-EB2964C2D30A}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
     <col min="2" max="2" width="35" style="1" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="54.42578125" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="59.1796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="54.453125" customWidth="1"/>
+    <col min="5" max="5" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>59</v>
       </c>
@@ -1528,7 +1985,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1545,7 +2002,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -1559,7 +2016,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -1573,7 +2030,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -1587,7 +2044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -1601,7 +2058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1615,7 +2072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -1629,7 +2086,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1643,7 +2100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -1657,7 +2114,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -1674,7 +2131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -1691,7 +2148,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1708,7 +2165,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -1722,7 +2179,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1736,7 +2193,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1750,7 +2207,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1764,7 +2221,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1778,7 +2235,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1792,7 +2249,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1806,7 +2263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1820,7 +2277,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1834,7 +2291,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1848,7 +2305,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1862,7 +2319,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -1876,7 +2333,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1890,7 +2347,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1904,7 +2361,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1918,7 +2375,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -1932,7 +2389,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1946,7 +2403,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1960,7 +2417,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1974,7 +2431,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1988,7 +2445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -2002,7 +2459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -2016,7 +2473,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -2030,7 +2487,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -2044,7 +2501,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2058,7 +2515,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>70</v>
       </c>
@@ -2072,7 +2529,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>70</v>
       </c>
@@ -2086,7 +2543,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>70</v>
       </c>
@@ -2100,7 +2557,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2114,7 +2571,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>76</v>
       </c>
@@ -2128,7 +2585,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>76</v>
       </c>
@@ -2142,7 +2599,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>76</v>
       </c>
@@ -2156,7 +2613,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>76</v>
       </c>
@@ -2170,7 +2627,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>76</v>
       </c>
@@ -2184,7 +2641,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>76</v>
       </c>
@@ -2199,9 +2656,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E48" xr:uid="{DB9FF7A4-C762-4C9E-945E-EB2964C2D30A}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2220,18 +2679,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE58F8B-44BD-49A5-9D8F-9E9F63A9F484}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="55.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="40.26953125" customWidth="1"/>
+    <col min="3" max="3" width="55.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -2254,7 +2713,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -2277,7 +2736,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -2300,7 +2759,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>99</v>
       </c>
@@ -2323,7 +2782,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -2346,7 +2805,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>110</v>
       </c>
@@ -2371,334 +2830,404 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08614373-5B5F-4011-B856-9A0C064934E2}">
-  <dimension ref="A1:I82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" customWidth="1"/>
-    <col min="6" max="6" width="35.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="41.85546875" customWidth="1"/>
-    <col min="10" max="10" width="47.140625" customWidth="1"/>
+    <col min="1" max="1" width="42.1796875" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="50.1796875" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" customWidth="1"/>
+    <col min="6" max="6" width="35.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" customWidth="1"/>
+    <col min="9" max="9" width="41.81640625" customWidth="1"/>
+    <col min="10" max="10" width="47.1796875" customWidth="1"/>
+    <col min="11" max="11" width="86.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="8" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F2" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="E4" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>273</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="F11" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="J12" t="s">
+        <v>285</v>
+      </c>
+      <c r="K12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J13" t="s">
+        <v>315</v>
+      </c>
+      <c r="K13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>273</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>317</v>
+      </c>
+      <c r="K14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J15" t="s">
+        <v>285</v>
+      </c>
+      <c r="K15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="E16" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="J16" t="s">
+        <v>310</v>
+      </c>
+      <c r="K16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E17" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J17" t="s">
+        <v>310</v>
+      </c>
+      <c r="K17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -2717,8 +3246,14 @@
       <c r="I18" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -2737,8 +3272,14 @@
       <c r="I19" s="4" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>287</v>
+      </c>
+      <c r="K19" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -2757,8 +3298,14 @@
       <c r="I20" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -2775,10 +3322,16 @@
         <v>192</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="J21" t="s">
+        <v>291</v>
+      </c>
+      <c r="K21" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -2792,13 +3345,19 @@
         <v>165</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>293</v>
+      </c>
+      <c r="K22" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -2806,24 +3365,30 @@
         <v>43</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>165</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="J23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K23" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>118</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>168</v>
@@ -2832,13 +3397,19 @@
         <v>189</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="J24" t="s">
+        <v>297</v>
+      </c>
+      <c r="K24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -2846,24 +3417,30 @@
         <v>140</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>189</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="J25" t="s">
+        <v>299</v>
+      </c>
+      <c r="K25" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>159</v>
@@ -2872,21 +3449,27 @@
         <v>189</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="J26" t="s">
+        <v>301</v>
+      </c>
+      <c r="K26" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>118</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>165</v>
@@ -2895,18 +3478,24 @@
         <v>184</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="J27" t="s">
+        <v>304</v>
+      </c>
+      <c r="K27" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>165</v>
@@ -2915,18 +3504,24 @@
         <v>184</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="J28" t="s">
+        <v>304</v>
+      </c>
+      <c r="K28" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>118</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>210</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>165</v>
@@ -2935,15 +3530,51 @@
         <v>184</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="J29" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>236</v>
+      </c>
+      <c r="F30" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" t="s">
+        <v>184</v>
+      </c>
+      <c r="I30" t="s">
+        <v>222</v>
+      </c>
+      <c r="J30" t="s">
+        <v>285</v>
+      </c>
+      <c r="K30" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -2957,47 +3588,83 @@
         <v>80</v>
       </c>
       <c r="E31" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
         <v>183</v>
       </c>
       <c r="G31" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H31" t="s">
         <v>184</v>
       </c>
       <c r="I31" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31" t="s">
+        <v>342</v>
+      </c>
+      <c r="K31" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E32" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" t="s">
-        <v>183</v>
-      </c>
-      <c r="G32" t="s">
-        <v>224</v>
       </c>
       <c r="H32" t="s">
         <v>184</v>
       </c>
       <c r="I32" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="J32" t="s">
+        <v>344</v>
+      </c>
+      <c r="K32" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
         <v>159</v>
       </c>
       <c r="G33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H33" t="s">
         <v>184</v>
@@ -3005,64 +3672,136 @@
       <c r="I33" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" t="s">
+        <v>346</v>
+      </c>
+      <c r="K33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="G34" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="H34" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="I34" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" t="s">
+        <v>342</v>
+      </c>
+      <c r="K34" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="G35" t="s">
         <v>165</v>
       </c>
       <c r="H35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I35" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" t="s">
+        <v>349</v>
+      </c>
+      <c r="K35" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="G36" t="s">
         <v>165</v>
       </c>
       <c r="H36" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="I36" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" t="s">
+        <v>351</v>
+      </c>
+      <c r="K36" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" t="s">
         <v>165</v>
@@ -3073,30 +3812,66 @@
       <c r="I37" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" t="s">
+        <v>353</v>
+      </c>
+      <c r="K37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G38" t="s">
         <v>165</v>
       </c>
       <c r="H38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I38" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" t="s">
+        <v>285</v>
+      </c>
+      <c r="K38" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="G39" t="s">
         <v>165</v>
@@ -3107,25 +3882,46 @@
       <c r="I39" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" t="s">
+        <v>285</v>
+      </c>
+      <c r="K39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E40" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="F40" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="I40" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J40" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3139,47 +3935,83 @@
         <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
         <v>183</v>
       </c>
       <c r="G41" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H41" t="s">
         <v>184</v>
       </c>
       <c r="I41" t="s">
+        <v>224</v>
+      </c>
+      <c r="J41" t="s">
+        <v>287</v>
+      </c>
+      <c r="K41" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" t="s">
+        <v>225</v>
+      </c>
+      <c r="F42" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
-        <v>122</v>
-      </c>
-      <c r="F42" t="s">
-        <v>183</v>
-      </c>
-      <c r="G42" t="s">
-        <v>224</v>
       </c>
       <c r="H42" t="s">
         <v>184</v>
       </c>
       <c r="I42" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="J42" t="s">
+        <v>323</v>
+      </c>
+      <c r="K42" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E43" t="s">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="F43" t="s">
         <v>159</v>
       </c>
       <c r="G43" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H43" t="s">
         <v>184</v>
@@ -3187,67 +4019,139 @@
       <c r="I43" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" t="s">
+        <v>310</v>
+      </c>
+      <c r="K43" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E44" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="F44" t="s">
         <v>159</v>
       </c>
       <c r="G44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H44" t="s">
         <v>184</v>
       </c>
       <c r="I44" t="s">
+        <v>273</v>
+      </c>
+      <c r="J44" t="s">
+        <v>326</v>
+      </c>
+      <c r="K44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" t="s">
+        <v>165</v>
+      </c>
+      <c r="H45" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E45" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" t="s">
-        <v>159</v>
-      </c>
-      <c r="G45" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" t="s">
-        <v>184</v>
-      </c>
       <c r="I45" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="J45" t="s">
+        <v>328</v>
+      </c>
+      <c r="K45" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E46" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="H46" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="I46" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" t="s">
+        <v>331</v>
+      </c>
+      <c r="K46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G47" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
         <v>129</v>
@@ -3255,16 +4159,34 @@
       <c r="I47" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" t="s">
+        <v>333</v>
+      </c>
+      <c r="K47" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="H48" t="s">
         <v>129</v>
@@ -3272,13 +4194,31 @@
       <c r="I48" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" t="s">
+        <v>335</v>
+      </c>
+      <c r="K48" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G49" t="s">
         <v>189</v>
@@ -3289,42 +4229,84 @@
       <c r="I49" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" t="s">
+        <v>337</v>
+      </c>
+      <c r="K49" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="G50" t="s">
         <v>189</v>
       </c>
       <c r="H50" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I50" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="J50" t="s">
+        <v>339</v>
+      </c>
+      <c r="K50" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E51" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="F51" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="H51" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="I51" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K51" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>114</v>
       </c>
@@ -3334,59 +4316,116 @@
       <c r="C52" t="s">
         <v>156</v>
       </c>
+      <c r="D52" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E52" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
         <v>183</v>
       </c>
       <c r="G52" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H52" t="s">
         <v>184</v>
       </c>
       <c r="I52" t="s">
+        <v>224</v>
+      </c>
+      <c r="J52" t="s">
+        <v>388</v>
+      </c>
+      <c r="K52" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>254</v>
+      </c>
+      <c r="F53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G53" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" t="s">
-        <v>183</v>
-      </c>
-      <c r="G53" t="s">
-        <v>224</v>
       </c>
       <c r="H53" t="s">
         <v>184</v>
       </c>
       <c r="I53" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="J53" t="s">
+        <v>389</v>
+      </c>
+      <c r="K53" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F54" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="G54" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="H54" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="I54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="J54" t="s">
+        <v>391</v>
+      </c>
+      <c r="K54" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E55" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="F55" t="s">
         <v>187</v>
@@ -3395,52 +4434,106 @@
         <v>165</v>
       </c>
       <c r="H55" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="I55" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="J55" t="s">
+        <v>393</v>
+      </c>
+      <c r="K55" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E56" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G56" t="s">
         <v>165</v>
       </c>
       <c r="H56" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I56" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" t="s">
+        <v>395</v>
+      </c>
+      <c r="K56" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="F57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G57" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="H57" t="s">
-        <v>259</v>
+        <v>129</v>
       </c>
       <c r="I57" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" t="s">
+        <v>397</v>
+      </c>
+      <c r="K57" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G58" t="s">
         <v>189</v>
@@ -3451,25 +4544,49 @@
       <c r="I58" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" t="s">
+        <v>399</v>
+      </c>
+      <c r="K58" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="E59" t="s">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="F59" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G59" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="H59" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="I59" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J59" t="s">
+        <v>285</v>
+      </c>
+      <c r="K59" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -3480,93 +4597,171 @@
         <v>79</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>142</v>
+        <v>279</v>
       </c>
       <c r="E60" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="G60" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H60" t="s">
         <v>184</v>
       </c>
       <c r="I60" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="J60" t="s">
+        <v>402</v>
+      </c>
+      <c r="K60" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="E61" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="F61" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="G61" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="H61" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="I61" t="s">
+        <v>257</v>
+      </c>
+      <c r="J61" t="s">
+        <v>403</v>
+      </c>
+      <c r="K61" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E62" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E62" t="s">
-        <v>257</v>
-      </c>
       <c r="F62" t="s">
-        <v>187</v>
+        <v>266</v>
       </c>
       <c r="G62" t="s">
         <v>165</v>
       </c>
       <c r="H62" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="I62" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="J62" t="s">
+        <v>405</v>
+      </c>
+      <c r="K62" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="E63" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F63" t="s">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="G63" t="s">
         <v>165</v>
       </c>
       <c r="H63" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I63" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="J63" t="s">
+        <v>402</v>
+      </c>
+      <c r="K63" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="E64" t="s">
-        <v>270</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G64" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H64" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="I64" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J64" t="s">
+        <v>285</v>
+      </c>
+      <c r="K64" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>145</v>
       </c>
@@ -3580,138 +4775,305 @@
         <v>146</v>
       </c>
       <c r="E65" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="F65" t="s">
         <v>183</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H65" t="s">
         <v>184</v>
       </c>
       <c r="I65" t="s">
+        <v>224</v>
+      </c>
+      <c r="J65" t="s">
+        <v>361</v>
+      </c>
+      <c r="K65" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" t="s">
+        <v>158</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" t="s">
+        <v>254</v>
+      </c>
+      <c r="F66" t="s">
+        <v>159</v>
+      </c>
+      <c r="G66" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E66" t="s">
-        <v>122</v>
-      </c>
-      <c r="F66" t="s">
-        <v>183</v>
-      </c>
-      <c r="G66" t="s">
-        <v>224</v>
       </c>
       <c r="H66" t="s">
         <v>184</v>
       </c>
       <c r="I66" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="J66" t="s">
+        <v>363</v>
+      </c>
+      <c r="K66" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" t="s">
+        <v>158</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="E67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F67" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="G67" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="H67" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="I67" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="J67" t="s">
+        <v>285</v>
+      </c>
+      <c r="K67" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="E68" t="s">
-        <v>257</v>
+        <v>147</v>
       </c>
       <c r="F68" t="s">
+        <v>199</v>
+      </c>
+      <c r="G68" t="s">
         <v>187</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>165</v>
-      </c>
-      <c r="H68" t="s">
-        <v>229</v>
       </c>
       <c r="I68" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68" t="s">
+        <v>367</v>
+      </c>
+      <c r="K68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C69" t="s">
+        <v>158</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G69" t="s">
-        <v>187</v>
-      </c>
-      <c r="H69" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="I69" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="J69" t="s">
+        <v>368</v>
+      </c>
+      <c r="K69" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="E70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G70" t="s">
         <v>189</v>
       </c>
+      <c r="H70" t="s">
+        <v>129</v>
+      </c>
       <c r="I70" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E71" t="s">
-        <v>149</v>
-      </c>
-      <c r="F71" t="s">
-        <v>200</v>
+        <v>261</v>
+      </c>
+      <c r="J70" t="s">
+        <v>370</v>
+      </c>
+      <c r="K70" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" t="s">
+        <v>105</v>
+      </c>
+      <c r="C71" t="s">
+        <v>158</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="G71" t="s">
-        <v>189</v>
-      </c>
-      <c r="H71" t="s">
-        <v>129</v>
+        <v>223</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="I71" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E72" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>159</v>
+      <c r="J71" t="s">
+        <v>372</v>
+      </c>
+      <c r="K71" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" t="s">
+        <v>158</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72" t="s">
+        <v>248</v>
+      </c>
+      <c r="F72" t="s">
+        <v>183</v>
       </c>
       <c r="G72" t="s">
+        <v>160</v>
+      </c>
+      <c r="H72" t="s">
+        <v>184</v>
+      </c>
+      <c r="I72" t="s">
+        <v>222</v>
+      </c>
+      <c r="J72" t="s">
+        <v>285</v>
+      </c>
+      <c r="K72" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" t="s">
+        <v>158</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E73" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" t="s">
+        <v>183</v>
+      </c>
+      <c r="G73" t="s">
+        <v>223</v>
+      </c>
+      <c r="H73" t="s">
+        <v>184</v>
+      </c>
+      <c r="I73" t="s">
         <v>224</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I72" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73" t="s">
+        <v>374</v>
+      </c>
+      <c r="K73" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>150</v>
       </c>
@@ -3725,158 +5087,243 @@
         <v>100</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F74" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="G74" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="H74" t="s">
         <v>184</v>
       </c>
       <c r="I74" t="s">
+        <v>246</v>
+      </c>
+      <c r="J74" t="s">
+        <v>375</v>
+      </c>
+      <c r="K74" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" t="s">
+        <v>159</v>
+      </c>
+      <c r="G75" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E75" t="s">
-        <v>122</v>
-      </c>
-      <c r="F75" t="s">
-        <v>183</v>
-      </c>
-      <c r="G75" t="s">
-        <v>224</v>
       </c>
       <c r="H75" t="s">
         <v>184</v>
       </c>
       <c r="I75" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="J75" t="s">
+        <v>285</v>
+      </c>
+      <c r="K75" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76" t="s">
+        <v>158</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="E76" t="s">
-        <v>246</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
+        <v>187</v>
+      </c>
+      <c r="G76" t="s">
+        <v>165</v>
+      </c>
+      <c r="H76" t="s">
+        <v>228</v>
+      </c>
+      <c r="I76" t="s">
+        <v>249</v>
+      </c>
+      <c r="J76" t="s">
+        <v>378</v>
+      </c>
+      <c r="K76" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77" t="s">
+        <v>158</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E77" t="s">
+        <v>151</v>
+      </c>
+      <c r="F77" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77" t="s">
+        <v>189</v>
+      </c>
+      <c r="H77" t="s">
+        <v>133</v>
+      </c>
+      <c r="I77" t="s">
+        <v>250</v>
+      </c>
+      <c r="J77" t="s">
+        <v>379</v>
+      </c>
+      <c r="K77" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" t="s">
+        <v>158</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E78" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78" t="s">
+        <v>178</v>
+      </c>
+      <c r="G78" t="s">
+        <v>189</v>
+      </c>
+      <c r="H78" t="s">
+        <v>133</v>
+      </c>
+      <c r="I78" t="s">
+        <v>251</v>
+      </c>
+      <c r="J78" t="s">
+        <v>381</v>
+      </c>
+      <c r="K78" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" t="s">
+        <v>158</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E79" t="s">
+        <v>153</v>
+      </c>
+      <c r="F79" t="s">
         <v>159</v>
       </c>
-      <c r="G76" t="s">
-        <v>224</v>
-      </c>
-      <c r="H76" t="s">
-        <v>184</v>
-      </c>
-      <c r="I76" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E77" t="s">
-        <v>138</v>
-      </c>
-      <c r="F77" t="s">
-        <v>159</v>
-      </c>
-      <c r="G77" t="s">
-        <v>224</v>
-      </c>
-      <c r="H77" t="s">
-        <v>184</v>
-      </c>
-      <c r="I77" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E78" t="s">
-        <v>126</v>
-      </c>
-      <c r="F78" t="s">
-        <v>187</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="G79" t="s">
         <v>165</v>
-      </c>
-      <c r="H78" t="s">
-        <v>229</v>
-      </c>
-      <c r="I78" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E79" t="s">
-        <v>151</v>
-      </c>
-      <c r="F79" t="s">
-        <v>178</v>
-      </c>
-      <c r="G79" t="s">
-        <v>189</v>
       </c>
       <c r="H79" t="s">
         <v>133</v>
       </c>
       <c r="I79" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="J79" t="s">
+        <v>383</v>
+      </c>
+      <c r="K79" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="E80" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F80" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G80" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="H80" t="s">
         <v>133</v>
       </c>
       <c r="I80" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="81" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E81" t="s">
-        <v>153</v>
-      </c>
-      <c r="F81" t="s">
-        <v>159</v>
-      </c>
-      <c r="G81" t="s">
-        <v>165</v>
-      </c>
-      <c r="H81" t="s">
-        <v>133</v>
-      </c>
-      <c r="I81" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="82" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E82" t="s">
-        <v>154</v>
-      </c>
-      <c r="F82" t="s">
-        <v>159</v>
-      </c>
-      <c r="G82" t="s">
-        <v>165</v>
-      </c>
-      <c r="H82" t="s">
-        <v>133</v>
-      </c>
-      <c r="I82" t="s">
-        <v>254</v>
+      <c r="J80" t="s">
+        <v>385</v>
+      </c>
+      <c r="K80" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3886,30 +5333,1679 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FCD6D9E-1FA2-4763-82EF-249F1F6B6D27}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="3" max="9" width="25.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" t="s">
+        <v>291</v>
+      </c>
+      <c r="I5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" t="s">
+        <v>295</v>
+      </c>
+      <c r="I7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" t="s">
+        <v>299</v>
+      </c>
+      <c r="I9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G12" t="s">
+        <v>303</v>
+      </c>
+      <c r="H12" t="s">
+        <v>304</v>
+      </c>
+      <c r="I12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" t="s">
+        <v>303</v>
+      </c>
+      <c r="H13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" t="s">
+        <v>285</v>
+      </c>
+      <c r="I14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" t="s">
+        <v>310</v>
+      </c>
+      <c r="I15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" t="s">
+        <v>165</v>
+      </c>
+      <c r="G16" t="s">
+        <v>192</v>
+      </c>
+      <c r="H16" t="s">
+        <v>310</v>
+      </c>
+      <c r="I16" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" t="s">
+        <v>285</v>
+      </c>
+      <c r="I17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" t="s">
+        <v>192</v>
+      </c>
+      <c r="H19" t="s">
+        <v>317</v>
+      </c>
+      <c r="I19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F20" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" t="s">
+        <v>282</v>
+      </c>
+      <c r="H20" t="s">
+        <v>283</v>
+      </c>
+      <c r="I20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" t="s">
+        <v>320</v>
+      </c>
+      <c r="H21" t="s">
+        <v>285</v>
+      </c>
+      <c r="I21" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G22" t="s">
+        <v>320</v>
+      </c>
+      <c r="H22" t="s">
+        <v>287</v>
+      </c>
+      <c r="I22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" t="s">
+        <v>223</v>
+      </c>
+      <c r="G23" t="s">
+        <v>320</v>
+      </c>
+      <c r="H23" t="s">
+        <v>323</v>
+      </c>
+      <c r="I23" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" t="s">
+        <v>320</v>
+      </c>
+      <c r="H24" t="s">
+        <v>310</v>
+      </c>
+      <c r="I24" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>272</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" t="s">
+        <v>223</v>
+      </c>
+      <c r="G25" t="s">
+        <v>320</v>
+      </c>
+      <c r="H25" t="s">
+        <v>326</v>
+      </c>
+      <c r="I25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" t="s">
+        <v>228</v>
+      </c>
+      <c r="H26" t="s">
+        <v>328</v>
+      </c>
+      <c r="I26" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G27" t="s">
+        <v>330</v>
+      </c>
+      <c r="H27" t="s">
+        <v>331</v>
+      </c>
+      <c r="I27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" t="s">
+        <v>330</v>
+      </c>
+      <c r="H28" t="s">
+        <v>333</v>
+      </c>
+      <c r="I28" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" t="s">
+        <v>199</v>
+      </c>
+      <c r="F29" t="s">
+        <v>189</v>
+      </c>
+      <c r="G29" t="s">
+        <v>330</v>
+      </c>
+      <c r="H29" t="s">
+        <v>335</v>
+      </c>
+      <c r="I29" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" t="s">
+        <v>330</v>
+      </c>
+      <c r="H30" t="s">
+        <v>337</v>
+      </c>
+      <c r="I30" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" t="s">
+        <v>330</v>
+      </c>
+      <c r="H31" t="s">
+        <v>339</v>
+      </c>
+      <c r="I31" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" t="s">
+        <v>320</v>
+      </c>
+      <c r="H32" t="s">
+        <v>285</v>
+      </c>
+      <c r="I32" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" t="s">
+        <v>223</v>
+      </c>
+      <c r="G33" t="s">
+        <v>320</v>
+      </c>
+      <c r="H33" t="s">
+        <v>342</v>
+      </c>
+      <c r="I33" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" t="s">
+        <v>223</v>
+      </c>
+      <c r="G34" t="s">
+        <v>320</v>
+      </c>
+      <c r="H34" t="s">
+        <v>344</v>
+      </c>
+      <c r="I34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" t="s">
+        <v>320</v>
+      </c>
+      <c r="H35" t="s">
+        <v>346</v>
+      </c>
+      <c r="I35" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" t="s">
+        <v>165</v>
+      </c>
+      <c r="G36" t="s">
+        <v>228</v>
+      </c>
+      <c r="H36" t="s">
+        <v>342</v>
+      </c>
+      <c r="I36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" t="s">
+        <v>165</v>
+      </c>
+      <c r="G37" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" t="s">
+        <v>349</v>
+      </c>
+      <c r="I37" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" t="s">
+        <v>199</v>
+      </c>
+      <c r="F38" t="s">
+        <v>165</v>
+      </c>
+      <c r="G38" t="s">
+        <v>330</v>
+      </c>
+      <c r="H38" t="s">
+        <v>351</v>
+      </c>
+      <c r="I38" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39" t="s">
+        <v>165</v>
+      </c>
+      <c r="G39" t="s">
+        <v>330</v>
+      </c>
+      <c r="H39" t="s">
+        <v>353</v>
+      </c>
+      <c r="I39" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" t="s">
+        <v>165</v>
+      </c>
+      <c r="G40" t="s">
+        <v>131</v>
+      </c>
+      <c r="H40" t="s">
+        <v>285</v>
+      </c>
+      <c r="I40" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" t="s">
+        <v>285</v>
+      </c>
+      <c r="I41" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" t="s">
+        <v>281</v>
+      </c>
+      <c r="F42" t="s">
+        <v>276</v>
+      </c>
+      <c r="G42" t="s">
+        <v>282</v>
+      </c>
+      <c r="H42" t="s">
+        <v>283</v>
+      </c>
+      <c r="I42" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" t="s">
+        <v>358</v>
+      </c>
+      <c r="E43" t="s">
+        <v>183</v>
+      </c>
+      <c r="F43" t="s">
+        <v>160</v>
+      </c>
+      <c r="G43" t="s">
+        <v>359</v>
+      </c>
+      <c r="H43" t="s">
+        <v>285</v>
+      </c>
+      <c r="I43" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" t="s">
+        <v>359</v>
+      </c>
+      <c r="H44" t="s">
+        <v>361</v>
+      </c>
+      <c r="I44" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C45" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G45" t="s">
+        <v>359</v>
+      </c>
+      <c r="H45" t="s">
+        <v>363</v>
+      </c>
+      <c r="I45" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C46" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" t="s">
+        <v>223</v>
+      </c>
+      <c r="G46" t="s">
+        <v>359</v>
+      </c>
+      <c r="H46" t="s">
+        <v>285</v>
+      </c>
+      <c r="I46" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C47" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47" t="s">
+        <v>366</v>
+      </c>
+      <c r="E47" t="s">
+        <v>187</v>
+      </c>
+      <c r="F47" t="s">
+        <v>165</v>
+      </c>
+      <c r="G47" t="s">
+        <v>228</v>
+      </c>
+      <c r="H47" t="s">
+        <v>367</v>
+      </c>
+      <c r="I47" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" t="s">
+        <v>199</v>
+      </c>
+      <c r="F48" t="s">
+        <v>165</v>
+      </c>
+      <c r="G48" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" t="s">
+        <v>368</v>
+      </c>
+      <c r="I48" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="49" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C49" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" t="s">
+        <v>199</v>
+      </c>
+      <c r="F49" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" t="s">
+        <v>133</v>
+      </c>
+      <c r="H49" t="s">
+        <v>370</v>
+      </c>
+      <c r="I49" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C50" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" t="s">
+        <v>199</v>
+      </c>
+      <c r="F50" t="s">
+        <v>189</v>
+      </c>
+      <c r="G50" t="s">
+        <v>330</v>
+      </c>
+      <c r="H50" t="s">
+        <v>372</v>
+      </c>
+      <c r="I50" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="51" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F51" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" t="s">
+        <v>359</v>
+      </c>
+      <c r="H51" t="s">
+        <v>285</v>
+      </c>
+      <c r="I51" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" t="s">
+        <v>223</v>
+      </c>
+      <c r="G52" t="s">
+        <v>359</v>
+      </c>
+      <c r="H52" t="s">
+        <v>374</v>
+      </c>
+      <c r="I52" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="53" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" t="s">
+        <v>245</v>
+      </c>
+      <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>223</v>
+      </c>
+      <c r="G53" t="s">
+        <v>359</v>
+      </c>
+      <c r="H53" t="s">
+        <v>375</v>
+      </c>
+      <c r="I53" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
+        <v>223</v>
+      </c>
+      <c r="G54" t="s">
+        <v>359</v>
+      </c>
+      <c r="H54" t="s">
+        <v>285</v>
+      </c>
+      <c r="I54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="55" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C55" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" t="s">
+        <v>165</v>
+      </c>
+      <c r="G55" t="s">
+        <v>228</v>
+      </c>
+      <c r="H55" t="s">
+        <v>378</v>
+      </c>
+      <c r="I55" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="56" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" t="s">
+        <v>151</v>
+      </c>
+      <c r="E56" t="s">
+        <v>178</v>
+      </c>
+      <c r="F56" t="s">
+        <v>189</v>
+      </c>
+      <c r="G56" t="s">
+        <v>133</v>
+      </c>
+      <c r="H56" t="s">
+        <v>379</v>
+      </c>
+      <c r="I56" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="57" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" t="s">
+        <v>178</v>
+      </c>
+      <c r="F57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G57" t="s">
+        <v>133</v>
+      </c>
+      <c r="H57" t="s">
+        <v>381</v>
+      </c>
+      <c r="I57" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="58" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C58" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" t="s">
+        <v>165</v>
+      </c>
+      <c r="G58" t="s">
+        <v>133</v>
+      </c>
+      <c r="H58" t="s">
+        <v>383</v>
+      </c>
+      <c r="I58" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="59" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C59" t="s">
+        <v>150</v>
+      </c>
+      <c r="D59" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>165</v>
+      </c>
+      <c r="G59" t="s">
+        <v>133</v>
+      </c>
+      <c r="H59" t="s">
+        <v>385</v>
+      </c>
+      <c r="I59" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="60" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C60" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" t="s">
+        <v>157</v>
+      </c>
+      <c r="E60" t="s">
+        <v>183</v>
+      </c>
+      <c r="F60" t="s">
+        <v>160</v>
+      </c>
+      <c r="G60" t="s">
+        <v>320</v>
+      </c>
+      <c r="H60" t="s">
+        <v>285</v>
+      </c>
+      <c r="I60" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="61" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" t="s">
+        <v>223</v>
+      </c>
+      <c r="G61" t="s">
+        <v>320</v>
+      </c>
+      <c r="H61" t="s">
+        <v>388</v>
+      </c>
+      <c r="I61" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C62" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" t="s">
+        <v>254</v>
+      </c>
+      <c r="E62" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s">
+        <v>223</v>
+      </c>
+      <c r="G62" t="s">
+        <v>320</v>
+      </c>
+      <c r="H62" t="s">
+        <v>389</v>
+      </c>
+      <c r="I62" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="63" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C63" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" t="s">
+        <v>187</v>
+      </c>
+      <c r="F63" t="s">
+        <v>165</v>
+      </c>
+      <c r="G63" t="s">
+        <v>228</v>
+      </c>
+      <c r="H63" t="s">
+        <v>391</v>
+      </c>
+      <c r="I63" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="64" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64" t="s">
+        <v>187</v>
+      </c>
+      <c r="F64" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" t="s">
+        <v>228</v>
+      </c>
+      <c r="H64" t="s">
+        <v>393</v>
+      </c>
+      <c r="I64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" t="s">
+        <v>195</v>
+      </c>
+      <c r="F65" t="s">
+        <v>165</v>
+      </c>
+      <c r="G65" t="s">
+        <v>228</v>
+      </c>
+      <c r="H65" t="s">
+        <v>395</v>
+      </c>
+      <c r="I65" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="66" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" t="s">
+        <v>143</v>
+      </c>
+      <c r="E66" t="s">
+        <v>199</v>
+      </c>
+      <c r="F66" t="s">
+        <v>189</v>
+      </c>
+      <c r="G66" t="s">
+        <v>330</v>
+      </c>
+      <c r="H66" t="s">
+        <v>397</v>
+      </c>
+      <c r="I66" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="67" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" t="s">
+        <v>199</v>
+      </c>
+      <c r="F67" t="s">
+        <v>189</v>
+      </c>
+      <c r="G67" t="s">
+        <v>330</v>
+      </c>
+      <c r="H67" t="s">
+        <v>399</v>
+      </c>
+      <c r="I67" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" t="s">
+        <v>263</v>
+      </c>
+      <c r="E68" t="s">
+        <v>183</v>
+      </c>
+      <c r="F68" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" t="s">
+        <v>359</v>
+      </c>
+      <c r="H68" t="s">
+        <v>285</v>
+      </c>
+      <c r="I68" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D69" t="s">
+        <v>245</v>
+      </c>
+      <c r="E69" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" t="s">
+        <v>223</v>
+      </c>
+      <c r="G69" t="s">
+        <v>359</v>
+      </c>
+      <c r="H69" t="s">
+        <v>402</v>
+      </c>
+      <c r="I69" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="70" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" t="s">
+        <v>256</v>
+      </c>
+      <c r="E70" t="s">
+        <v>187</v>
+      </c>
+      <c r="F70" t="s">
+        <v>165</v>
+      </c>
+      <c r="G70" t="s">
+        <v>228</v>
+      </c>
+      <c r="H70" t="s">
+        <v>403</v>
+      </c>
+      <c r="I70" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="71" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C71" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71" t="s">
+        <v>265</v>
+      </c>
+      <c r="E71" t="s">
+        <v>266</v>
+      </c>
+      <c r="F71" t="s">
+        <v>165</v>
+      </c>
+      <c r="G71" t="s">
+        <v>267</v>
+      </c>
+      <c r="H71" t="s">
+        <v>405</v>
+      </c>
+      <c r="I71" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C72" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" t="s">
+        <v>269</v>
+      </c>
+      <c r="E72" t="s">
+        <v>178</v>
+      </c>
+      <c r="F72" t="s">
+        <v>165</v>
+      </c>
+      <c r="G72" t="s">
+        <v>270</v>
+      </c>
+      <c r="H72" t="s">
+        <v>402</v>
+      </c>
+      <c r="I72" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
